--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/arica-y-parinacota.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3443.58</v>
+        <v>3435.07</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>23267.37</v>
+        <v>22789.18</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>41235.28</v>
+        <v>41026.39</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>21660.04</v>
+        <v>21534.67</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/arica-y-parinacota.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3459-133-CM26</t>
+          <t>5855-40-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3435.07</v>
+        <v>652.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3340-175-CM26</t>
+          <t>3459-152-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>VENTIA SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.798.686-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>22789.18</v>
+        <v>600.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3483-243-CM26</t>
+          <t>2585-3621-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>COMERCIAL ANDES SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>77.765.995-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>41026.39</v>
+        <v>11938.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2585-710-CM26</t>
+          <t>3459-133-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,6 +752,189 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
+        <v>3435.07</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3340-175-CM26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>65.286.850-9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>22789.18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3483-243-CM26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>65.286.830-4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ADM SPA.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>77.909.208-9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>41026.39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2585-710-CM26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>21534.67</v>
       </c>
     </row>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/arica-y-parinacota.xlsx
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/arica-y-parinacota.xlsx
@@ -562,7 +562,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/arica-y-parinacota.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
